--- a/artfynd/A 13034-2024 artfynd.xlsx
+++ b/artfynd/A 13034-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85776955</v>
+        <v>85776951</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718586.2354463905</v>
+        <v>718714</v>
       </c>
       <c r="R2" t="n">
-        <v>7111501.682692387</v>
+        <v>7111438</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-05-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-05-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>85776953</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718596.8538091501</v>
+        <v>718597</v>
       </c>
       <c r="R3" t="n">
-        <v>7111463.341496</v>
+        <v>7111463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-05-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-05-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>85776957</v>
+        <v>85776955</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718607.0987813923</v>
+        <v>718586</v>
       </c>
       <c r="R4" t="n">
-        <v>7111517.6470335</v>
+        <v>7111502</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-05-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-05-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>85776963</v>
+        <v>85776957</v>
       </c>
       <c r="B5" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718737.5931065594</v>
+        <v>718607</v>
       </c>
       <c r="R5" t="n">
-        <v>7111874.680268469</v>
+        <v>7111518</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2020-05-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-05-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>85776962</v>
+        <v>85776959</v>
       </c>
       <c r="B6" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,39 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rambo, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718670.1927262754</v>
+        <v>718611</v>
       </c>
       <c r="R6" t="n">
-        <v>7111508.479715922</v>
+        <v>7111542</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,19 +1147,9 @@
           <t>2020-05-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-05-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>85776959</v>
+        <v>85776963</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718610.6863788659</v>
+        <v>718738</v>
       </c>
       <c r="R7" t="n">
-        <v>7111541.616880743</v>
+        <v>7111875</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1248,9 @@
           <t>2020-05-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-05-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,50 +1281,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>85776961</v>
+        <v>85776962</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rambo, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718631.8386381621</v>
+        <v>718670</v>
       </c>
       <c r="R8" t="n">
-        <v>7111534.763154042</v>
+        <v>7111508</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,19 +1354,9 @@
           <t>2020-05-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-05-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 13034-2024 artfynd.xlsx
+++ b/artfynd/A 13034-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85776951</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85776953</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85776955</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85776957</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85776959</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85776963</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,8 +1419,22 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85776962</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>